--- a/excel_files/蕭豪興.xlsx
+++ b/excel_files/蕭豪興.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478C38F0-0FB0-47DE-A099-13B23C032C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C78F12-7E41-4C44-831C-BC5B6C5F0C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5854D81B-5B7B-4871-9FA3-56C4511C9373}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>拉配線</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,10 @@
   </si>
   <si>
     <t>會議</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +95,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -106,12 +110,6 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="3">
@@ -157,12 +155,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,98 +476,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0FA30E-FDBB-4AD6-9BBA-7E5C7E4F325B}">
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1"/>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
